--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q40_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.10_b0.10_x0.30_Q40_LO.xlsx
@@ -455,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02814861730730032</v>
+        <v>0.01443414244609968</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02814861730730032</v>
+        <v>0.01443414244609968</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01424032688440133</v>
+        <v>0.008354681612565328</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02606575218385453</v>
+        <v>0.01322995054517905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02606575218385453</v>
+        <v>0.01322995054517905</v>
       </c>
       <c r="D3" t="n">
-        <v>0.009012266043530245</v>
+        <v>0.006484022150453944</v>
       </c>
     </row>
     <row r="4">
@@ -483,13 +483,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03154126055485362</v>
+        <v>0.01615793669852568</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03154126055485362</v>
+        <v>0.01615793669852568</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006170087219146672</v>
+        <v>0.006036204550318607</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04922177477768944</v>
+        <v>0.02573236848474729</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04922177477768944</v>
+        <v>0.02573236848474729</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008554681491862615</v>
+        <v>0.008288216813531377</v>
       </c>
     </row>
     <row r="6">
@@ -511,13 +511,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.07493222400450736</v>
+        <v>0.03921206567331495</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07493222400450736</v>
+        <v>0.03921206567331495</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01744067775212148</v>
+        <v>0.0144369827911434</v>
       </c>
     </row>
     <row r="7">
@@ -525,13 +525,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1019468844197882</v>
+        <v>0.0530797919375409</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1019468844197882</v>
+        <v>0.0530797919375409</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01188651996614466</v>
+        <v>0.01620201150733527</v>
       </c>
     </row>
     <row r="8">
@@ -539,13 +539,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1378226123910175</v>
+        <v>0.07178263648750108</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1378226123910175</v>
+        <v>0.07178263648750108</v>
       </c>
       <c r="D8" t="n">
-        <v>0.007616110395973381</v>
+        <v>0.02070652935132841</v>
       </c>
     </row>
     <row r="9">
@@ -553,13 +553,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.172653149287661</v>
+        <v>0.09014841610166861</v>
       </c>
       <c r="C9" t="n">
-        <v>0.172653149287661</v>
+        <v>0.09014841610166861</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01147071175752164</v>
+        <v>0.02721464105317</v>
       </c>
     </row>
     <row r="10">
@@ -567,13 +567,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1977279264148081</v>
+        <v>0.1033418087016317</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1977279264148081</v>
+        <v>0.1033418087016317</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01361608261070967</v>
+        <v>0.03163964430162811</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +581,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2103877004800731</v>
+        <v>0.1098646559835099</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2103877004800731</v>
+        <v>0.1098646559835099</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01663852054934739</v>
+        <v>0.03348105780617326</v>
       </c>
     </row>
     <row r="12">
@@ -595,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2101514969682185</v>
+        <v>0.1095871539395589</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2101514969682185</v>
+        <v>0.1095871539395589</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01889801371045047</v>
+        <v>0.03324607290780978</v>
       </c>
     </row>
     <row r="13">
@@ -609,13 +609,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2040182699539714</v>
+        <v>0.1063266686820006</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2040182699539714</v>
+        <v>0.1063266686820006</v>
       </c>
       <c r="D13" t="n">
-        <v>0.01910973607494774</v>
+        <v>0.0315189780523452</v>
       </c>
     </row>
     <row r="14">
@@ -623,13 +623,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1955886416425803</v>
+        <v>0.1019781999043783</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1955886416425803</v>
+        <v>0.1019781999043783</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01849204558207557</v>
+        <v>0.02958071621599146</v>
       </c>
     </row>
     <row r="15">
@@ -637,13 +637,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1826858321417394</v>
+        <v>0.09529236884480996</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1826858321417394</v>
+        <v>0.09529236884480996</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01790077301215142</v>
+        <v>0.02685882995357938</v>
       </c>
     </row>
     <row r="16">
@@ -651,13 +651,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1794483556854094</v>
+        <v>0.09367728504601165</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1794483556854094</v>
+        <v>0.09367728504601165</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01859705234952773</v>
+        <v>0.02622126166300587</v>
       </c>
     </row>
     <row r="17">
@@ -665,13 +665,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.168584858762561</v>
+        <v>0.08806285423474039</v>
       </c>
       <c r="C17" t="n">
-        <v>0.168584858762561</v>
+        <v>0.08806285423474039</v>
       </c>
       <c r="D17" t="n">
-        <v>0.01827373772141925</v>
+        <v>0.02437467073456507</v>
       </c>
     </row>
     <row r="18">
@@ -679,13 +679,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1620785988122843</v>
+        <v>0.08473211563838695</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1620785988122843</v>
+        <v>0.08473211563838695</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01886555051416545</v>
+        <v>0.02359814908144264</v>
       </c>
     </row>
     <row r="19">
@@ -693,13 +693,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1664796863534011</v>
+        <v>0.08707429782865676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1664796863534011</v>
+        <v>0.08707429782865676</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02065106481523999</v>
+        <v>0.02326420365834991</v>
       </c>
     </row>
     <row r="20">
@@ -707,13 +707,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1565931274323611</v>
+        <v>0.08196690627320467</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1565931274323611</v>
+        <v>0.08196690627320467</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02178499188978428</v>
+        <v>0.0226735933911719</v>
       </c>
     </row>
     <row r="21">
@@ -721,13 +721,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.153097451451264</v>
+        <v>0.08040607299699788</v>
       </c>
       <c r="C21" t="n">
-        <v>0.153097451451264</v>
+        <v>0.08040607299699788</v>
       </c>
       <c r="D21" t="n">
-        <v>0.02263158313325044</v>
+        <v>0.02211453125593837</v>
       </c>
     </row>
   </sheetData>
